--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 22,10,26 мррсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 22,10,26 мррсч пок зпф.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F9D58E-9D1E-4468-B7BB-9DFAE630FCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96A52BC-3227-4300-8D06-BE33549F27C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AH$85</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="190">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -591,6 +599,9 @@
   <si>
     <t>кратность 168шт</t>
   </si>
+  <si>
+    <t>26,10,</t>
+  </si>
 </sst>
 </file>
 
@@ -1341,7 +1352,9 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
       <c r="AC4" s="7"/>
-      <c r="AD4" s="9"/>
+      <c r="AD4" s="9" t="s">
+        <v>189</v>
+      </c>
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
@@ -2645,7 +2658,7 @@
         <v>42.2</v>
       </c>
       <c r="Q17" s="5">
-        <f t="shared" ref="Q16:Q17" si="6">14*P17-O17-F17</f>
+        <f t="shared" ref="Q17" si="6">14*P17-O17-F17</f>
         <v>143.80000000000007</v>
       </c>
       <c r="R17" s="5">
@@ -3285,7 +3298,7 @@
         <v>55.6</v>
       </c>
       <c r="Q23" s="5">
-        <f t="shared" ref="Q23:Q27" si="8">14*P23-O23-F23</f>
+        <f t="shared" ref="Q23:Q26" si="8">14*P23-O23-F23</f>
         <v>90.399999999999977</v>
       </c>
       <c r="R23" s="5">
@@ -4532,7 +4545,7 @@
         <v>83.2</v>
       </c>
       <c r="Q34" s="5">
-        <f t="shared" ref="Q29:Q35" si="14">14*P34-O34-F34</f>
+        <f t="shared" ref="Q34" si="14">14*P34-O34-F34</f>
         <v>671.8</v>
       </c>
       <c r="R34" s="5">
@@ -5094,7 +5107,7 @@
         <v>31</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" ref="Q37:Q63" si="24">14*P39-O39-F39</f>
+        <f t="shared" ref="Q39:Q62" si="24">14*P39-O39-F39</f>
         <v>84</v>
       </c>
       <c r="R39" s="5">
@@ -8643,7 +8656,7 @@
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="25">E70-K70</f>
+        <f t="shared" ref="L70:L85" si="25">E70-K70</f>
         <v>339</v>
       </c>
       <c r="M70" s="1"/>
@@ -8656,7 +8669,7 @@
         <v>67.8</v>
       </c>
       <c r="Q70" s="5">
-        <f t="shared" ref="Q69:Q71" si="27">14*P70-O70-F70</f>
+        <f t="shared" ref="Q70:Q71" si="27">14*P70-O70-F70</f>
         <v>642.19999999999993</v>
       </c>
       <c r="R70" s="5">
@@ -8664,7 +8677,7 @@
         <v>672</v>
       </c>
       <c r="S70" s="1">
-        <f t="shared" ref="S70:S101" si="28">(F70+O70+R70)/P70</f>
+        <f t="shared" ref="S70:S85" si="28">(F70+O70+R70)/P70</f>
         <v>14.43952802359882</v>
       </c>
       <c r="T70" s="1">
